--- a/template/5.29/净值 - 副本 (4).xlsx
+++ b/template/5.29/净值 - 副本 (4).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22095" activeTab="5"/>
+    <workbookView windowHeight="22095" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="量化一-结算数据" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="196">
   <si>
     <t>日期</t>
   </si>
@@ -49,414 +49,411 @@
     <t>回撤-无返息</t>
   </si>
   <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>2025/02/24</t>
+  </si>
+  <si>
+    <t>2025/02/25</t>
+  </si>
+  <si>
+    <t>-0.002%</t>
+  </si>
+  <si>
+    <t>2025/02/26</t>
+  </si>
+  <si>
+    <t>2025/02/27</t>
+  </si>
+  <si>
+    <t>2025/02/28</t>
+  </si>
+  <si>
+    <t>-0.048%</t>
+  </si>
+  <si>
+    <t>2025/03/03</t>
+  </si>
+  <si>
+    <t>2025/03/04</t>
+  </si>
+  <si>
+    <t>2025/03/05</t>
+  </si>
+  <si>
+    <t>-0.018%</t>
+  </si>
+  <si>
+    <t>2025/03/06</t>
+  </si>
+  <si>
+    <t>-0.046%</t>
+  </si>
+  <si>
+    <t>2025/03/07</t>
+  </si>
+  <si>
+    <t>-0.02%</t>
+  </si>
+  <si>
+    <t>2025/03/10</t>
+  </si>
+  <si>
+    <t>2025/03/11</t>
+  </si>
+  <si>
+    <t>-0.064%</t>
+  </si>
+  <si>
+    <t>2025/03/12</t>
+  </si>
+  <si>
+    <t>-0.066%</t>
+  </si>
+  <si>
+    <t>2025/03/13</t>
+  </si>
+  <si>
+    <t>-0.099%</t>
+  </si>
+  <si>
+    <t>2025/03/14</t>
+  </si>
+  <si>
+    <t>-0.233%</t>
+  </si>
+  <si>
+    <t>2025/03/17</t>
+  </si>
+  <si>
+    <t>-0.229%</t>
+  </si>
+  <si>
+    <t>2025/03/18</t>
+  </si>
+  <si>
+    <t>-0.228%</t>
+  </si>
+  <si>
+    <t>2025/03/19</t>
+  </si>
+  <si>
+    <t>-0.224%</t>
+  </si>
+  <si>
+    <t>2025/03/20</t>
+  </si>
+  <si>
+    <t>-0.216%</t>
+  </si>
+  <si>
+    <t>2025/03/21</t>
+  </si>
+  <si>
+    <t>-0.206%</t>
+  </si>
+  <si>
+    <t>2025/03/24</t>
+  </si>
+  <si>
+    <t>-0.198%</t>
+  </si>
+  <si>
+    <t>2025/03/25</t>
+  </si>
+  <si>
+    <t>-0.205%</t>
+  </si>
+  <si>
+    <t>2025/03/26</t>
+  </si>
+  <si>
+    <t>-0.194%</t>
+  </si>
+  <si>
+    <t>2025/03/27</t>
+  </si>
+  <si>
+    <t>-0.191%</t>
+  </si>
+  <si>
+    <t>2025/03/28</t>
+  </si>
+  <si>
+    <t>-0.179%</t>
+  </si>
+  <si>
+    <t>2025/03/31</t>
+  </si>
+  <si>
+    <t>-0.175%</t>
+  </si>
+  <si>
+    <t>2025/04/01</t>
+  </si>
+  <si>
+    <t>-0.131%</t>
+  </si>
+  <si>
+    <t>2025/04/02</t>
+  </si>
+  <si>
+    <t>-0.126%</t>
+  </si>
+  <si>
+    <t>2025/04/03</t>
+  </si>
+  <si>
+    <t>-0.091%</t>
+  </si>
+  <si>
+    <t>2025/04/07</t>
+  </si>
+  <si>
+    <t>-0.481%</t>
+  </si>
+  <si>
+    <t>2025/04/08</t>
+  </si>
+  <si>
+    <t>-0.417%</t>
+  </si>
+  <si>
+    <t>2025/04/09</t>
+  </si>
+  <si>
+    <t>-0.415%</t>
+  </si>
+  <si>
+    <t>2025/04/10</t>
+  </si>
+  <si>
+    <t>-0.411%</t>
+  </si>
+  <si>
+    <t>2025/04/11</t>
+  </si>
+  <si>
+    <t>-0.377%</t>
+  </si>
+  <si>
+    <t>2025/04/14</t>
+  </si>
+  <si>
+    <t>-0.129%</t>
+  </si>
+  <si>
+    <t>2025/04/15</t>
+  </si>
+  <si>
+    <t>-0.124%</t>
+  </si>
+  <si>
+    <t>2025/04/16</t>
+  </si>
+  <si>
+    <t>-0.115%</t>
+  </si>
+  <si>
+    <t>2025/04/17</t>
+  </si>
+  <si>
+    <t>-0.178%</t>
+  </si>
+  <si>
+    <t>2025/04/18</t>
+  </si>
+  <si>
+    <t>-0.281%</t>
+  </si>
+  <si>
+    <t>2025/04/21</t>
+  </si>
+  <si>
+    <t>-0.262%</t>
+  </si>
+  <si>
+    <t>2025/04/22</t>
+  </si>
+  <si>
+    <t>-0.257%</t>
+  </si>
+  <si>
+    <t>2025/04/23</t>
+  </si>
+  <si>
+    <t>-0.22%</t>
+  </si>
+  <si>
+    <t>2025/04/24</t>
+  </si>
+  <si>
+    <t>-0.345%</t>
+  </si>
+  <si>
+    <t>2025/04/25</t>
+  </si>
+  <si>
+    <t>-0.437%</t>
+  </si>
+  <si>
+    <t>2025/04/28</t>
+  </si>
+  <si>
+    <t>-0.585%</t>
+  </si>
+  <si>
+    <t>2025/04/29</t>
+  </si>
+  <si>
+    <t>-0.573%</t>
+  </si>
+  <si>
+    <t>2025/04/30</t>
+  </si>
+  <si>
+    <t>-0.527%</t>
+  </si>
+  <si>
+    <t>2025/05/06</t>
+  </si>
+  <si>
+    <t>2025/05/07</t>
+  </si>
+  <si>
+    <t>-0.325%</t>
+  </si>
+  <si>
+    <t>2025/05/08</t>
+  </si>
+  <si>
+    <t>-0.272%</t>
+  </si>
+  <si>
+    <t>2025/05/09</t>
+  </si>
+  <si>
+    <t>-0.326%</t>
+  </si>
+  <si>
+    <t>2025/05/12</t>
+  </si>
+  <si>
+    <t>-0.3%</t>
+  </si>
+  <si>
+    <t>2025/05/13</t>
+  </si>
+  <si>
+    <t>-0.286%</t>
+  </si>
+  <si>
+    <t>2025/05/14</t>
+  </si>
+  <si>
+    <t>-0.287%</t>
+  </si>
+  <si>
+    <t>2025/05/15</t>
+  </si>
+  <si>
+    <t>-0.283%</t>
+  </si>
+  <si>
+    <t>2025/05/16</t>
+  </si>
+  <si>
+    <t>-0.274%</t>
+  </si>
+  <si>
+    <t>2025/05/19</t>
+  </si>
+  <si>
+    <t>2025/05/20</t>
+  </si>
+  <si>
+    <t>-0.239%</t>
+  </si>
+  <si>
+    <t>2025/05/21</t>
+  </si>
+  <si>
+    <t>-0.243%</t>
+  </si>
+  <si>
+    <t>2025/05/22</t>
+  </si>
+  <si>
+    <t>-0.278%</t>
+  </si>
+  <si>
+    <t>2025/05/23</t>
+  </si>
+  <si>
+    <t>-0.406%</t>
+  </si>
+  <si>
+    <t>2025/05/26</t>
+  </si>
+  <si>
+    <t>-0.384%</t>
+  </si>
+  <si>
+    <t>2025/05/27</t>
+  </si>
+  <si>
+    <t>-0.35%</t>
+  </si>
+  <si>
+    <t>2025/05/28</t>
+  </si>
+  <si>
+    <t>-0.336%</t>
+  </si>
+  <si>
+    <t>-0.391%</t>
+  </si>
+  <si>
+    <t>-0.387%</t>
+  </si>
+  <si>
+    <t>-0.354%</t>
+  </si>
+  <si>
+    <t>-0.107%</t>
+  </si>
+  <si>
+    <t>-0.105%</t>
+  </si>
+  <si>
+    <t>-0.096%</t>
+  </si>
+  <si>
+    <t>-0.159%</t>
+  </si>
+  <si>
+    <t>-0.238%</t>
+  </si>
+  <si>
+    <t>-0.201%</t>
+  </si>
+  <si>
+    <t>-0.324%</t>
+  </si>
+  <si>
+    <t>-0.419%</t>
+  </si>
+  <si>
+    <t>-0.566%</t>
+  </si>
+  <si>
+    <t>-0.553%</t>
+  </si>
+  <si>
     <t>0%</t>
   </si>
   <si>
-    <t>2025/02/24</t>
-  </si>
-  <si>
-    <t>2025/02/25</t>
-  </si>
-  <si>
-    <t>-0.002%</t>
-  </si>
-  <si>
-    <t>2025/02/26</t>
-  </si>
-  <si>
-    <t>2025/02/27</t>
-  </si>
-  <si>
-    <t>2025/02/28</t>
-  </si>
-  <si>
-    <t>-0.048%</t>
-  </si>
-  <si>
-    <t>2025/03/03</t>
-  </si>
-  <si>
-    <t>2025/03/04</t>
-  </si>
-  <si>
-    <t>2025/03/05</t>
-  </si>
-  <si>
-    <t>-0.018%</t>
-  </si>
-  <si>
-    <t>2025/03/06</t>
-  </si>
-  <si>
-    <t>-0.046%</t>
-  </si>
-  <si>
-    <t>2025/03/07</t>
-  </si>
-  <si>
-    <t>-0.02%</t>
-  </si>
-  <si>
-    <t>2025/03/10</t>
-  </si>
-  <si>
-    <t>2025/03/11</t>
-  </si>
-  <si>
-    <t>-0.064%</t>
-  </si>
-  <si>
-    <t>2025/03/12</t>
-  </si>
-  <si>
-    <t>-0.066%</t>
-  </si>
-  <si>
-    <t>2025/03/13</t>
-  </si>
-  <si>
-    <t>-0.099%</t>
-  </si>
-  <si>
-    <t>2025/03/14</t>
-  </si>
-  <si>
-    <t>-0.233%</t>
-  </si>
-  <si>
-    <t>2025/03/17</t>
-  </si>
-  <si>
-    <t>-0.229%</t>
-  </si>
-  <si>
-    <t>2025/03/18</t>
-  </si>
-  <si>
-    <t>-0.228%</t>
-  </si>
-  <si>
-    <t>2025/03/19</t>
-  </si>
-  <si>
-    <t>-0.224%</t>
-  </si>
-  <si>
-    <t>2025/03/20</t>
-  </si>
-  <si>
-    <t>-0.216%</t>
-  </si>
-  <si>
-    <t>2025/03/21</t>
-  </si>
-  <si>
-    <t>-0.206%</t>
-  </si>
-  <si>
-    <t>2025/03/24</t>
-  </si>
-  <si>
-    <t>-0.198%</t>
-  </si>
-  <si>
-    <t>2025/03/25</t>
-  </si>
-  <si>
-    <t>-0.205%</t>
-  </si>
-  <si>
-    <t>2025/03/26</t>
-  </si>
-  <si>
-    <t>-0.194%</t>
-  </si>
-  <si>
-    <t>2025/03/27</t>
-  </si>
-  <si>
-    <t>-0.191%</t>
-  </si>
-  <si>
-    <t>2025/03/28</t>
-  </si>
-  <si>
-    <t>-0.179%</t>
-  </si>
-  <si>
-    <t>2025/03/31</t>
-  </si>
-  <si>
-    <t>-0.175%</t>
-  </si>
-  <si>
-    <t>2025/04/01</t>
-  </si>
-  <si>
-    <t>-0.131%</t>
-  </si>
-  <si>
-    <t>2025/04/02</t>
-  </si>
-  <si>
-    <t>-0.126%</t>
-  </si>
-  <si>
-    <t>2025/04/03</t>
-  </si>
-  <si>
-    <t>-0.091%</t>
-  </si>
-  <si>
-    <t>2025/04/07</t>
-  </si>
-  <si>
-    <t>-0.481%</t>
-  </si>
-  <si>
-    <t>2025/04/08</t>
-  </si>
-  <si>
-    <t>-0.417%</t>
-  </si>
-  <si>
-    <t>2025/04/09</t>
-  </si>
-  <si>
-    <t>-0.415%</t>
-  </si>
-  <si>
-    <t>2025/04/10</t>
-  </si>
-  <si>
-    <t>-0.411%</t>
-  </si>
-  <si>
-    <t>2025/04/11</t>
-  </si>
-  <si>
-    <t>-0.377%</t>
-  </si>
-  <si>
-    <t>2025/04/14</t>
-  </si>
-  <si>
-    <t>-0.129%</t>
-  </si>
-  <si>
-    <t>2025/04/15</t>
-  </si>
-  <si>
-    <t>-0.124%</t>
-  </si>
-  <si>
-    <t>2025/04/16</t>
-  </si>
-  <si>
-    <t>-0.115%</t>
-  </si>
-  <si>
-    <t>2025/04/17</t>
-  </si>
-  <si>
-    <t>-0.178%</t>
-  </si>
-  <si>
-    <t>2025/04/18</t>
-  </si>
-  <si>
-    <t>-0.281%</t>
-  </si>
-  <si>
-    <t>2025/04/21</t>
-  </si>
-  <si>
-    <t>-0.262%</t>
-  </si>
-  <si>
-    <t>2025/04/22</t>
-  </si>
-  <si>
-    <t>-0.257%</t>
-  </si>
-  <si>
-    <t>2025/04/23</t>
-  </si>
-  <si>
-    <t>-0.22%</t>
-  </si>
-  <si>
-    <t>2025/04/24</t>
-  </si>
-  <si>
-    <t>-0.345%</t>
-  </si>
-  <si>
-    <t>2025/04/25</t>
-  </si>
-  <si>
-    <t>-0.437%</t>
-  </si>
-  <si>
-    <t>2025/04/28</t>
-  </si>
-  <si>
-    <t>-0.585%</t>
-  </si>
-  <si>
-    <t>2025/04/29</t>
-  </si>
-  <si>
-    <t>-0.573%</t>
-  </si>
-  <si>
-    <t>2025/04/30</t>
-  </si>
-  <si>
-    <t>-0.527%</t>
-  </si>
-  <si>
-    <t>2025/05/06</t>
-  </si>
-  <si>
-    <t>2025/05/07</t>
-  </si>
-  <si>
-    <t>-0.325%</t>
-  </si>
-  <si>
-    <t>2025/05/08</t>
-  </si>
-  <si>
-    <t>-0.272%</t>
-  </si>
-  <si>
-    <t>2025/05/09</t>
-  </si>
-  <si>
-    <t>-0.326%</t>
-  </si>
-  <si>
-    <t>2025/05/12</t>
-  </si>
-  <si>
-    <t>-0.3%</t>
-  </si>
-  <si>
-    <t>2025/05/13</t>
-  </si>
-  <si>
-    <t>-0.286%</t>
-  </si>
-  <si>
-    <t>2025/05/14</t>
-  </si>
-  <si>
-    <t>-0.287%</t>
-  </si>
-  <si>
-    <t>2025/05/15</t>
-  </si>
-  <si>
-    <t>-0.283%</t>
-  </si>
-  <si>
-    <t>2025/05/16</t>
-  </si>
-  <si>
-    <t>-0.274%</t>
-  </si>
-  <si>
-    <t>2025/05/19</t>
-  </si>
-  <si>
-    <t>2025/05/20</t>
-  </si>
-  <si>
-    <t>-0.239%</t>
-  </si>
-  <si>
-    <t>2025/05/21</t>
-  </si>
-  <si>
-    <t>-0.243%</t>
-  </si>
-  <si>
-    <t>2025/05/22</t>
-  </si>
-  <si>
-    <t>-0.278%</t>
-  </si>
-  <si>
-    <t>2025/05/23</t>
-  </si>
-  <si>
-    <t>-0.406%</t>
-  </si>
-  <si>
-    <t>2025/05/26</t>
-  </si>
-  <si>
-    <t>-0.384%</t>
-  </si>
-  <si>
-    <t>2025/05/27</t>
-  </si>
-  <si>
-    <t>-0.35%</t>
-  </si>
-  <si>
-    <t>2025/05/28</t>
-  </si>
-  <si>
-    <t>-0.336%</t>
-  </si>
-  <si>
-    <t>2025/05/29</t>
-  </si>
-  <si>
-    <t>-0.343%</t>
-  </si>
-  <si>
-    <t>-0.391%</t>
-  </si>
-  <si>
-    <t>-0.387%</t>
-  </si>
-  <si>
-    <t>-0.354%</t>
-  </si>
-  <si>
-    <t>-0.107%</t>
-  </si>
-  <si>
-    <t>-0.105%</t>
-  </si>
-  <si>
-    <t>-0.096%</t>
-  </si>
-  <si>
-    <t>-0.159%</t>
-  </si>
-  <si>
-    <t>-0.238%</t>
-  </si>
-  <si>
-    <t>-0.201%</t>
-  </si>
-  <si>
-    <t>-0.324%</t>
-  </si>
-  <si>
-    <t>-0.419%</t>
-  </si>
-  <si>
-    <t>-0.566%</t>
-  </si>
-  <si>
-    <t>-0.553%</t>
-  </si>
-  <si>
     <t>-0.113%</t>
   </si>
   <si>
@@ -556,9 +553,6 @@
     <t>-1.744%</t>
   </si>
   <si>
-    <t>-1.4257%</t>
-  </si>
-  <si>
     <t>-0.0946%</t>
   </si>
   <si>
@@ -626,9 +620,6 @@
   </si>
   <si>
     <t>-2.1277%</t>
-  </si>
-  <si>
-    <t>-1.5462%</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1600,7 @@
     <col min="3" max="3" width="15.25" style="10" customWidth="1"/>
     <col min="4" max="4" width="15.875" style="5" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="5"/>
+    <col min="6" max="16384" width="9" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2735,21 +2726,11 @@
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B67" s="5">
-        <v>0.99661</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D67" s="5">
-        <v>0.99661</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>127</v>
-      </c>
+      <c r="A67" s="12"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67"/>
+      <c r="E67"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3338,13 +3319,13 @@
         <v>0.99613</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D34">
         <v>0.99613</v>
       </c>
       <c r="E34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3355,13 +3336,13 @@
         <v>0.99617</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D35">
         <v>0.99617</v>
       </c>
       <c r="E35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3372,13 +3353,13 @@
         <v>0.9965</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D36">
         <v>0.9965</v>
       </c>
       <c r="E36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3389,13 +3370,13 @@
         <v>0.99897</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D37">
         <v>0.99897</v>
       </c>
       <c r="E37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3406,13 +3387,13 @@
         <v>0.99899</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D38">
         <v>0.99899</v>
       </c>
       <c r="E38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3423,13 +3404,13 @@
         <v>0.99908</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D39">
         <v>0.99908</v>
       </c>
       <c r="E39" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3440,13 +3421,13 @@
         <v>0.99845</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D40">
         <v>0.99845</v>
       </c>
       <c r="E40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3491,13 +3472,13 @@
         <v>0.99766</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D43">
         <v>0.99766</v>
       </c>
       <c r="E43" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -3508,13 +3489,13 @@
         <v>0.99803</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D44">
         <v>0.99803</v>
       </c>
       <c r="E44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -3525,13 +3506,13 @@
         <v>0.9968</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D45">
         <v>0.9968</v>
       </c>
       <c r="E45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3542,13 +3523,13 @@
         <v>0.99585</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D46">
         <v>0.99585</v>
       </c>
       <c r="E46" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -3559,13 +3540,13 @@
         <v>0.99438</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D47">
         <v>0.99438</v>
       </c>
       <c r="E47" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -3576,13 +3557,13 @@
         <v>0.99451</v>
       </c>
       <c r="C48" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D48">
         <v>0.99451</v>
       </c>
       <c r="E48" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -3891,22 +3872,10 @@
         <v>125</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B67">
-        <v>0.99661</v>
-      </c>
-      <c r="C67" t="s">
-        <v>127</v>
-      </c>
-      <c r="D67">
-        <v>0.99661</v>
-      </c>
-      <c r="E67" t="s">
-        <v>127</v>
-      </c>
+    <row r="67" spans="1:3">
+      <c r="A67" s="7"/>
+      <c r="B67"/>
+      <c r="C67"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3951,13 +3920,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3968,13 +3937,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3985,13 +3954,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4002,13 +3971,13 @@
         <v>1.00006</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D5">
         <v>1.00006</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4019,13 +3988,13 @@
         <v>0.99893</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6">
         <v>0.99893</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4036,13 +4005,13 @@
         <v>0.99799</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7">
         <v>0.99799</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4053,13 +4022,13 @@
         <v>0.99735</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8">
         <v>0.99735</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4070,13 +4039,13 @@
         <v>0.99697</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9">
         <v>0.99697</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4087,13 +4056,13 @@
         <v>0.99549</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10">
         <v>0.99549</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4104,13 +4073,13 @@
         <v>0.99481</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11">
         <v>0.99481</v>
       </c>
       <c r="E11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4121,13 +4090,13 @@
         <v>0.99504</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12">
         <v>0.99504</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4138,13 +4107,13 @@
         <v>0.99543</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13">
         <v>0.99543</v>
       </c>
       <c r="E13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4155,13 +4124,13 @@
         <v>0.99225</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14">
         <v>0.99225</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4172,13 +4141,13 @@
         <v>0.99901</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15">
         <v>0.99901</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4189,13 +4158,13 @@
         <v>1.00088</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D16">
         <v>1.00088</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4206,13 +4175,13 @@
         <v>1.00384</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D17">
         <v>1.00384</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4223,13 +4192,13 @@
         <v>1.00286</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D18">
         <v>1.00286</v>
       </c>
       <c r="E18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4240,13 +4209,13 @@
         <v>1.00359</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D19">
         <v>1.00359</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4257,13 +4226,13 @@
         <v>1.00333</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D20">
         <v>1.00333</v>
       </c>
       <c r="E20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4274,13 +4243,13 @@
         <v>1.00132</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D21">
         <v>1.00132</v>
       </c>
       <c r="E21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4291,13 +4260,13 @@
         <v>0.99975</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D22">
         <v>0.99975</v>
       </c>
       <c r="E22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4308,13 +4277,13 @@
         <v>0.99922</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D23">
         <v>0.99922</v>
       </c>
       <c r="E23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -4325,13 +4294,13 @@
         <v>1.00056</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D24">
         <v>1.00056</v>
       </c>
       <c r="E24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -4342,13 +4311,13 @@
         <v>1.0006</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D25">
         <v>1.0006</v>
       </c>
       <c r="E25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -4359,13 +4328,13 @@
         <v>1.00096</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D26">
         <v>1.00096</v>
       </c>
       <c r="E26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4376,13 +4345,13 @@
         <v>0.9998</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D27">
         <v>0.9998</v>
       </c>
       <c r="E27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -4393,13 +4362,13 @@
         <v>1.002</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D28">
         <v>1.002</v>
       </c>
       <c r="E28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4410,13 +4379,13 @@
         <v>1.00457</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D29">
         <v>1.00457</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -4427,13 +4396,13 @@
         <v>1.00494</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D30">
         <v>1.00494</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -4444,13 +4413,13 @@
         <v>1.00596</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D31">
         <v>1.00596</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -4461,13 +4430,13 @@
         <v>1.00818</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D32">
         <v>1.00818</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -4478,13 +4447,13 @@
         <v>1.00916</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D33">
         <v>1.00916</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -4495,13 +4464,13 @@
         <v>1.00869</v>
       </c>
       <c r="C34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D34">
         <v>1.00869</v>
       </c>
       <c r="E34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -4512,13 +4481,13 @@
         <v>1.00774</v>
       </c>
       <c r="C35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D35">
         <v>1.00774</v>
       </c>
       <c r="E35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -4529,13 +4498,13 @@
         <v>1.00763</v>
       </c>
       <c r="C36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D36">
         <v>1.00763</v>
       </c>
       <c r="E36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -4546,13 +4515,13 @@
         <v>1.01353</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D37">
         <v>1.01353</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -4563,13 +4532,13 @@
         <v>1.01567</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D38">
         <v>1.01567</v>
       </c>
       <c r="E38" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4580,13 +4549,13 @@
         <v>1.02409</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D39">
         <v>1.02409</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -4597,13 +4566,13 @@
         <v>1.02353</v>
       </c>
       <c r="C40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D40">
         <v>1.02353</v>
       </c>
       <c r="E40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -4614,13 +4583,13 @@
         <v>1.01869</v>
       </c>
       <c r="C41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D41">
         <v>1.01869</v>
       </c>
       <c r="E41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -4631,13 +4600,13 @@
         <v>1.01625</v>
       </c>
       <c r="C42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D42">
         <v>1.01625</v>
       </c>
       <c r="E42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -4648,13 +4617,13 @@
         <v>1.01695</v>
       </c>
       <c r="C43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D43">
         <v>1.01695</v>
       </c>
       <c r="E43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -4665,13 +4634,13 @@
         <v>1.01901</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D44">
         <v>1.01901</v>
       </c>
       <c r="E44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4682,13 +4651,13 @@
         <v>1.01473</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D45">
         <v>1.01473</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -4699,13 +4668,13 @@
         <v>1.00963</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D46">
         <v>1.00963</v>
       </c>
       <c r="E46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -4716,13 +4685,13 @@
         <v>1.00841</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D47">
         <v>1.00841</v>
       </c>
       <c r="E47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4733,13 +4702,13 @@
         <v>1.00601</v>
       </c>
       <c r="C48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D48">
         <v>1.00601</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4750,31 +4719,19 @@
         <v>1.00623</v>
       </c>
       <c r="C49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D49">
         <v>1.00623</v>
       </c>
       <c r="E49" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50">
-        <v>1.00949</v>
-      </c>
-      <c r="C50" t="s">
-        <v>174</v>
-      </c>
-      <c r="D50">
-        <v>1.00949</v>
-      </c>
-      <c r="E50" t="s">
-        <v>174</v>
-      </c>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="7"/>
+      <c r="B50"/>
+      <c r="C50"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4818,13 +4775,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4835,13 +4792,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4852,13 +4809,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4869,13 +4826,13 @@
         <v>1.00006</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D5">
         <v>1.00006</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4886,13 +4843,13 @@
         <v>0.99893</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6">
         <v>0.99893</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4903,13 +4860,13 @@
         <v>0.99799</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7">
         <v>0.99799</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4920,13 +4877,13 @@
         <v>0.99735</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8">
         <v>0.99735</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4937,13 +4894,13 @@
         <v>0.99697</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9">
         <v>0.99697</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4954,13 +4911,13 @@
         <v>0.99549</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10">
         <v>0.99549</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4971,13 +4928,13 @@
         <v>0.99481</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11">
         <v>0.99481</v>
       </c>
       <c r="E11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4988,13 +4945,13 @@
         <v>0.99504</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12">
         <v>0.99504</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5005,13 +4962,13 @@
         <v>0.99543</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13">
         <v>0.99543</v>
       </c>
       <c r="E13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5022,13 +4979,13 @@
         <v>0.99225</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14">
         <v>0.99225</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5039,13 +4996,13 @@
         <v>0.99901</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15">
         <v>0.99901</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5056,13 +5013,13 @@
         <v>1.00088</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D16">
         <v>1.00088</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5073,13 +5030,13 @@
         <v>1.00351</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D17">
         <v>1.00351</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5090,13 +5047,13 @@
         <v>1.00397</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D18">
         <v>1.00397</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5107,13 +5064,13 @@
         <v>1.0042</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D19">
         <v>1.0042</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5124,13 +5081,13 @@
         <v>1.00325</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D20">
         <v>1.00325</v>
       </c>
       <c r="E20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5141,13 +5098,13 @@
         <v>1.00045</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D21">
         <v>1.00045</v>
       </c>
       <c r="E21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5158,13 +5115,13 @@
         <v>0.99963</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D22">
         <v>0.99963</v>
       </c>
       <c r="E22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5175,13 +5132,13 @@
         <v>0.99994</v>
       </c>
       <c r="C23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D23">
         <v>0.99994</v>
       </c>
       <c r="E23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5192,13 +5149,13 @@
         <v>1.00073</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D24">
         <v>1.00073</v>
       </c>
       <c r="E24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5209,13 +5166,13 @@
         <v>1.00146</v>
       </c>
       <c r="C25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D25">
         <v>1.00146</v>
       </c>
       <c r="E25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5226,13 +5183,13 @@
         <v>1.0023</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D26">
         <v>1.0023</v>
       </c>
       <c r="E26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5243,13 +5200,13 @@
         <v>1.00159</v>
       </c>
       <c r="C27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D27">
         <v>1.00159</v>
       </c>
       <c r="E27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5260,13 +5217,13 @@
         <v>1.00396</v>
       </c>
       <c r="C28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D28">
         <v>1.00396</v>
       </c>
       <c r="E28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5277,13 +5234,13 @@
         <v>1.00616</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D29">
         <v>1.00616</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5294,13 +5251,13 @@
         <v>1.00573</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D30">
         <v>1.00573</v>
       </c>
       <c r="E30" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5311,13 +5268,13 @@
         <v>1.00707</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D31">
         <v>1.00707</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5328,13 +5285,13 @@
         <v>1.00825</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D32">
         <v>1.00825</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5345,13 +5302,13 @@
         <v>1.00923</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D33">
         <v>1.00923</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -5362,13 +5319,13 @@
         <v>1.00802</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D34">
         <v>1.00802</v>
       </c>
       <c r="E34" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -5379,13 +5336,13 @@
         <v>1.00687</v>
       </c>
       <c r="C35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D35">
         <v>1.00687</v>
       </c>
       <c r="E35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5396,13 +5353,13 @@
         <v>1.00785</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D36">
         <v>1.00785</v>
       </c>
       <c r="E36" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -5413,13 +5370,13 @@
         <v>1.01623</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D37">
         <v>1.01623</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -5430,13 +5387,13 @@
         <v>1.01723</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D38">
         <v>1.01723</v>
       </c>
       <c r="E38" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -5447,13 +5404,13 @@
         <v>1.02833</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D39">
         <v>1.02833</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -5464,13 +5421,13 @@
         <v>1.02249</v>
       </c>
       <c r="C40" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D40">
         <v>1.02249</v>
       </c>
       <c r="E40" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -5481,13 +5438,13 @@
         <v>1.01655</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D41">
         <v>1.01655</v>
       </c>
       <c r="E41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -5498,13 +5455,13 @@
         <v>1.01685</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D42">
         <v>1.01685</v>
       </c>
       <c r="E42" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -5515,13 +5472,13 @@
         <v>1.01575</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D43">
         <v>1.01575</v>
       </c>
       <c r="E43" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -5532,13 +5489,13 @@
         <v>1.01935</v>
       </c>
       <c r="C44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D44">
         <v>1.01935</v>
       </c>
       <c r="E44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -5549,13 +5506,13 @@
         <v>1.01442</v>
       </c>
       <c r="C45" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D45">
         <v>1.01442</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -5566,13 +5523,13 @@
         <v>1.00768</v>
       </c>
       <c r="C46" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D46">
         <v>1.00768</v>
       </c>
       <c r="E46" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -5583,13 +5540,13 @@
         <v>1.0093</v>
       </c>
       <c r="C47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D47">
         <v>1.0093</v>
       </c>
       <c r="E47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -5600,13 +5557,13 @@
         <v>1.00721</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D48">
         <v>1.00721</v>
       </c>
       <c r="E48" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -5617,31 +5574,19 @@
         <v>1.00645</v>
       </c>
       <c r="C49" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D49">
         <v>1.00645</v>
       </c>
       <c r="E49" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50">
-        <v>1.01243</v>
-      </c>
-      <c r="C50" t="s">
-        <v>198</v>
-      </c>
-      <c r="D50">
-        <v>1.01243</v>
-      </c>
-      <c r="E50" t="s">
-        <v>198</v>
-      </c>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="7"/>
+      <c r="B50"/>
+      <c r="C50"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5681,13 +5626,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5698,13 +5643,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5715,13 +5660,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5732,13 +5677,13 @@
         <v>1.00006</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D5">
         <v>1.00006</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5749,13 +5694,13 @@
         <v>0.99893</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6">
         <v>0.99893</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5766,13 +5711,13 @@
         <v>0.99799</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7">
         <v>0.99799</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5783,13 +5728,13 @@
         <v>0.99735</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8">
         <v>0.99735</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5800,13 +5745,13 @@
         <v>0.99697</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9">
         <v>0.99697</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5817,13 +5762,13 @@
         <v>0.99549</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10">
         <v>0.99549</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5834,13 +5779,13 @@
         <v>0.99481</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11">
         <v>0.99481</v>
       </c>
       <c r="E11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5851,13 +5796,13 @@
         <v>0.99504</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12">
         <v>0.99504</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5868,13 +5813,13 @@
         <v>0.99543</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13">
         <v>0.99543</v>
       </c>
       <c r="E13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5885,13 +5830,13 @@
         <v>0.99225</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14">
         <v>0.99225</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5902,13 +5847,13 @@
         <v>0.99901</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15">
         <v>0.99901</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5919,13 +5864,13 @@
         <v>1.00088</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D16">
         <v>1.00088</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5936,13 +5881,13 @@
         <v>1.00384</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D17">
         <v>1.00384</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5953,13 +5898,13 @@
         <v>1.00286</v>
       </c>
       <c r="C18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D18">
         <v>1.00286</v>
       </c>
       <c r="E18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5970,13 +5915,13 @@
         <v>1.00359</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D19">
         <v>1.00359</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5987,13 +5932,13 @@
         <v>1.00333</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D20">
         <v>1.00333</v>
       </c>
       <c r="E20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6004,13 +5949,13 @@
         <v>1.00132</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D21">
         <v>1.00132</v>
       </c>
       <c r="E21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6021,13 +5966,13 @@
         <v>0.99975</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D22">
         <v>0.99975</v>
       </c>
       <c r="E22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6038,13 +5983,13 @@
         <v>0.99922</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D23">
         <v>0.99922</v>
       </c>
       <c r="E23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6055,13 +6000,13 @@
         <v>1.00056</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D24">
         <v>1.00056</v>
       </c>
       <c r="E24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6072,13 +6017,13 @@
         <v>1.0006</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D25">
         <v>1.0006</v>
       </c>
       <c r="E25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6089,13 +6034,13 @@
         <v>1.00096</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D26">
         <v>1.00096</v>
       </c>
       <c r="E26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6106,13 +6051,13 @@
         <v>0.9998</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D27">
         <v>0.9998</v>
       </c>
       <c r="E27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6123,13 +6068,13 @@
         <v>1.002</v>
       </c>
       <c r="C28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D28">
         <v>1.002</v>
       </c>
       <c r="E28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -6140,13 +6085,13 @@
         <v>1.00457</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D29">
         <v>1.00457</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -6157,13 +6102,13 @@
         <v>1.00494</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D30">
         <v>1.00494</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6174,13 +6119,13 @@
         <v>1.00596</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D31">
         <v>1.00596</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6191,13 +6136,13 @@
         <v>1.00818</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D32">
         <v>1.00818</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6208,13 +6153,13 @@
         <v>1.00916</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D33">
         <v>1.00916</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -6225,13 +6170,13 @@
         <v>1.00869</v>
       </c>
       <c r="C34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D34">
         <v>1.00869</v>
       </c>
       <c r="E34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -6242,13 +6187,13 @@
         <v>1.00774</v>
       </c>
       <c r="C35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D35">
         <v>1.00774</v>
       </c>
       <c r="E35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -6259,13 +6204,13 @@
         <v>1.00763</v>
       </c>
       <c r="C36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D36">
         <v>1.00763</v>
       </c>
       <c r="E36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6276,13 +6221,13 @@
         <v>1.01353</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D37">
         <v>1.01353</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6293,13 +6238,13 @@
         <v>1.01567</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D38">
         <v>1.01567</v>
       </c>
       <c r="E38" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6310,13 +6255,13 @@
         <v>1.02409</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D39">
         <v>1.02409</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6327,13 +6272,13 @@
         <v>1.02353</v>
       </c>
       <c r="C40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D40">
         <v>1.02353</v>
       </c>
       <c r="E40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6344,13 +6289,13 @@
         <v>1.01869</v>
       </c>
       <c r="C41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D41">
         <v>1.01869</v>
       </c>
       <c r="E41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -6361,13 +6306,13 @@
         <v>1.01625</v>
       </c>
       <c r="C42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D42">
         <v>1.01625</v>
       </c>
       <c r="E42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -6378,13 +6323,13 @@
         <v>1.01695</v>
       </c>
       <c r="C43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D43">
         <v>1.01695</v>
       </c>
       <c r="E43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -6395,13 +6340,13 @@
         <v>1.01901</v>
       </c>
       <c r="C44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D44">
         <v>1.01901</v>
       </c>
       <c r="E44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -6412,13 +6357,13 @@
         <v>1.01473</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D45">
         <v>1.01473</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -6429,13 +6374,13 @@
         <v>1.00963</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D46">
         <v>1.00963</v>
       </c>
       <c r="E46" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -6446,13 +6391,13 @@
         <v>1.00841</v>
       </c>
       <c r="C47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D47">
         <v>1.00841</v>
       </c>
       <c r="E47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6463,13 +6408,13 @@
         <v>1.00601</v>
       </c>
       <c r="C48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D48">
         <v>1.00601</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -6480,31 +6425,17 @@
         <v>1.00623</v>
       </c>
       <c r="C49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D49">
         <v>1.00623</v>
       </c>
       <c r="E49" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50">
-        <v>1.00949</v>
-      </c>
-      <c r="C50" t="s">
-        <v>174</v>
-      </c>
-      <c r="D50">
-        <v>1.00949</v>
-      </c>
-      <c r="E50" t="s">
-        <v>174</v>
-      </c>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6548,13 +6479,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6565,13 +6496,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6582,13 +6513,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6599,13 +6530,13 @@
         <v>1.00006</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D5">
         <v>1.00006</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6616,13 +6547,13 @@
         <v>0.99893</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6">
         <v>0.99893</v>
       </c>
       <c r="E6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6633,13 +6564,13 @@
         <v>0.99799</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7">
         <v>0.99799</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6650,13 +6581,13 @@
         <v>0.99735</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8">
         <v>0.99735</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6667,13 +6598,13 @@
         <v>0.99697</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9">
         <v>0.99697</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6684,13 +6615,13 @@
         <v>0.99549</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10">
         <v>0.99549</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6701,13 +6632,13 @@
         <v>0.99481</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11">
         <v>0.99481</v>
       </c>
       <c r="E11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6718,13 +6649,13 @@
         <v>0.99504</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12">
         <v>0.99504</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6735,13 +6666,13 @@
         <v>0.99543</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13">
         <v>0.99543</v>
       </c>
       <c r="E13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6752,13 +6683,13 @@
         <v>0.99225</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D14">
         <v>0.99225</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6769,13 +6700,13 @@
         <v>0.99901</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D15">
         <v>0.99901</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6786,13 +6717,13 @@
         <v>1.00088</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D16">
         <v>1.00088</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6803,13 +6734,13 @@
         <v>1.00351</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D17">
         <v>1.00351</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6820,13 +6751,13 @@
         <v>1.00397</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D18">
         <v>1.00397</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6837,13 +6768,13 @@
         <v>1.0042</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D19">
         <v>1.0042</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6854,13 +6785,13 @@
         <v>1.00325</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D20">
         <v>1.00325</v>
       </c>
       <c r="E20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6871,13 +6802,13 @@
         <v>1.00045</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D21">
         <v>1.00045</v>
       </c>
       <c r="E21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6888,13 +6819,13 @@
         <v>0.99963</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D22">
         <v>0.99963</v>
       </c>
       <c r="E22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6905,13 +6836,13 @@
         <v>0.99994</v>
       </c>
       <c r="C23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D23">
         <v>0.99994</v>
       </c>
       <c r="E23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6922,13 +6853,13 @@
         <v>1.00073</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D24">
         <v>1.00073</v>
       </c>
       <c r="E24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6939,13 +6870,13 @@
         <v>1.00146</v>
       </c>
       <c r="C25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D25">
         <v>1.00146</v>
       </c>
       <c r="E25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6956,13 +6887,13 @@
         <v>1.0023</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D26">
         <v>1.0023</v>
       </c>
       <c r="E26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6973,13 +6904,13 @@
         <v>1.00159</v>
       </c>
       <c r="C27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D27">
         <v>1.00159</v>
       </c>
       <c r="E27" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -6990,13 +6921,13 @@
         <v>1.00396</v>
       </c>
       <c r="C28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D28">
         <v>1.00396</v>
       </c>
       <c r="E28" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7007,13 +6938,13 @@
         <v>1.00616</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D29">
         <v>1.00616</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7024,13 +6955,13 @@
         <v>1.00573</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D30">
         <v>1.00573</v>
       </c>
       <c r="E30" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7041,13 +6972,13 @@
         <v>1.00707</v>
       </c>
       <c r="C31" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D31">
         <v>1.00707</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7058,13 +6989,13 @@
         <v>1.00825</v>
       </c>
       <c r="C32" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D32">
         <v>1.00825</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7075,13 +7006,13 @@
         <v>1.00923</v>
       </c>
       <c r="C33" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D33">
         <v>1.00923</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7092,13 +7023,13 @@
         <v>1.00802</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D34">
         <v>1.00802</v>
       </c>
       <c r="E34" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7109,13 +7040,13 @@
         <v>1.00687</v>
       </c>
       <c r="C35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D35">
         <v>1.00687</v>
       </c>
       <c r="E35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7126,13 +7057,13 @@
         <v>1.00785</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D36">
         <v>1.00785</v>
       </c>
       <c r="E36" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7143,13 +7074,13 @@
         <v>1.01623</v>
       </c>
       <c r="C37" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D37">
         <v>1.01623</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -7160,13 +7091,13 @@
         <v>1.01723</v>
       </c>
       <c r="C38" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D38">
         <v>1.01723</v>
       </c>
       <c r="E38" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -7177,13 +7108,13 @@
         <v>1.02833</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="D39">
         <v>1.02833</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -7194,13 +7125,13 @@
         <v>1.02249</v>
       </c>
       <c r="C40" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D40">
         <v>1.02249</v>
       </c>
       <c r="E40" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -7211,13 +7142,13 @@
         <v>1.01655</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D41">
         <v>1.01655</v>
       </c>
       <c r="E41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -7228,13 +7159,13 @@
         <v>1.01685</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D42">
         <v>1.01685</v>
       </c>
       <c r="E42" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -7245,13 +7176,13 @@
         <v>1.01575</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D43">
         <v>1.01575</v>
       </c>
       <c r="E43" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -7262,13 +7193,13 @@
         <v>1.01935</v>
       </c>
       <c r="C44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D44">
         <v>1.01935</v>
       </c>
       <c r="E44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -7279,13 +7210,13 @@
         <v>1.01442</v>
       </c>
       <c r="C45" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D45">
         <v>1.01442</v>
       </c>
       <c r="E45" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -7296,13 +7227,13 @@
         <v>1.00768</v>
       </c>
       <c r="C46" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D46">
         <v>1.00768</v>
       </c>
       <c r="E46" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -7313,13 +7244,13 @@
         <v>1.0093</v>
       </c>
       <c r="C47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D47">
         <v>1.0093</v>
       </c>
       <c r="E47" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -7330,13 +7261,13 @@
         <v>1.00721</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D48">
         <v>1.00721</v>
       </c>
       <c r="E48" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -7347,31 +7278,19 @@
         <v>1.00645</v>
       </c>
       <c r="C49" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D49">
         <v>1.00645</v>
       </c>
       <c r="E49" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50">
-        <v>1.01243</v>
-      </c>
-      <c r="C50" t="s">
-        <v>198</v>
-      </c>
-      <c r="D50">
-        <v>1.01243</v>
-      </c>
-      <c r="E50" t="s">
-        <v>198</v>
-      </c>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="7"/>
+      <c r="B50"/>
+      <c r="C50"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
